--- a/upload/cringe.xlsx
+++ b/upload/cringe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Assignments" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assignments'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assignments'!$A$1:$I$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,15 +419,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,21 +456,33 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>publish_date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>publish_time</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>move_folder</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>monetization</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/cringe.xlsx
+++ b/upload/cringe.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Assignments" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assignments'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assignments'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,18 +419,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,33 +454,24 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>publish_date</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>publish_date</t>
+          <t>publish_time</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>publish_time</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>move_folder</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>monetization</t>
+          <t>related_video</t>
         </is>
       </c>
     </row>
     <row r="2"/>
+    <row r="3"/>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>